--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:35</t>
+    <t xml:space="preserve">2026-09-24 01:25</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -793,7 +793,7 @@
         <v>-0.4</v>
       </c>
       <c r="D19" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="20">
@@ -804,10 +804,10 @@
         <v>25</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="D20" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="21">
@@ -821,7 +821,7 @@
         <v>-0.24</v>
       </c>
       <c r="D21" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="22">
@@ -835,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="D22" s="2" t="n">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="23">
@@ -860,7 +860,7 @@
         <v>31</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.34</v>
       </c>
       <c r="D24" s="2" t="n">
         <v>329</v>
@@ -874,7 +874,7 @@
         <v>31</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>0.17</v>
+        <v>0.19</v>
       </c>
       <c r="D25" s="2" t="n">
         <v>329</v>
@@ -888,7 +888,7 @@
         <v>31</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>-0.34</v>
+        <v>-0.27</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>329</v>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_arica_y_parinacota.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Migración</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Saldo migratorio</t>
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 01:25</t>
+    <t xml:space="preserve">2026-10-01 23:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_arica_y_parinacota.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_s_isapre_a_2022_arica_y_parinacota.xlsx
@@ -132,7 +132,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:07</t>
+    <t xml:space="preserve">2026-10-05 19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
